--- a/cleaned_orders/cleaned_跨8.xlsx
+++ b/cleaned_orders/cleaned_跨8.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,35 +439,40 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>标准佣金率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>店铺</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>内容形式</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>订单状态</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>SKU后四位</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>产品名称</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>标准佣金率</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>店铺</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>内容形式</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>订单状态</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>SourceID</t>
         </is>
@@ -481,11 +486,13 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026/6/4</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -494,35 +501,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>跨8</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8235</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>关节凝胶</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>跨8</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>未匹配负责人</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,11 +544,13 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026/6/4</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -545,35 +559,40 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>跨8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4619</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>足贴</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>跨8</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>视频</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>未匹配负责人</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
